--- a/src-tauri/samples/mame/05_mame_sample_map.xlsx
+++ b/src-tauri/samples/mame/05_mame_sample_map.xlsx
@@ -467,7 +467,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Q232A_r1</t>
+          <t>S65T_r1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Q232A_r2</t>
+          <t>S65T_r2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -491,7 +491,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Q232A_r3</t>
+          <t>S65T_r3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y233A_r1</t>
+          <t>Y66H_r1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -515,7 +515,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Y233A_r2</t>
+          <t>Y66H_r2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Y233A_r3</t>
+          <t>Y66H_r3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A40P_r1</t>
+          <t>T203Y_r1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -551,7 +551,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A40P_r2</t>
+          <t>T203Y_r2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A40P_r3</t>
+          <t>T203Y_r3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -575,7 +575,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E61Y_r1</t>
+          <t>F64L_r1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E61Y_r2</t>
+          <t>F64L_r2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E61Y_r3</t>
+          <t>F64L_r3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -611,7 +611,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L150V_r1</t>
+          <t>A206K_r1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L150V_r2</t>
+          <t>A206K_r2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L150V_r3</t>
+          <t>A206K_r3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A40P_E61Y_r1</t>
+          <t>S65A_r1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A40P_E61Y_r2</t>
+          <t>S65A_r2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A40P_E61Y_r3</t>
+          <t>S65A_r3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
